--- a/backtest_runs/20260410_193731/by_symbol/AGIC/AGIC.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/AGIC/AGIC.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="I4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>103388.32</v>
@@ -679,7 +679,7 @@
         <v>-6400.160000000003</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>96988.16</v>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="I9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>102664.32</v>
@@ -1047,7 +1047,7 @@
         <v>-1448</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>108630.08</v>
@@ -1093,7 +1093,7 @@
         <v>-28.95999999999424</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>108601.12</v>
@@ -1185,7 +1185,7 @@
         <v>-1361.119999999997</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>108977.6</v>
@@ -1231,7 +1231,7 @@
         <v>-2143.040000000006</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>106834.56</v>
@@ -1277,7 +1277,7 @@
         <v>-463.3599999999901</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>106371.2</v>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>111149.6</v>
@@ -1645,7 +1645,7 @@
         <v>-1563.840000000018</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>115232.96</v>
